--- a/exporters_master.xlsx
+++ b/exporters_master.xlsx
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Company Profile'!$A$1:$J$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Company Products'!$A$1:$H$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Companies'!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contacts'!$A$1:$D$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contacts'!$A$1:$D$386</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Product Match Audit'!$A$1:$G$549</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Certifications'!$A$1:$B$407</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Accreditations'!$A$1:$B$490</definedName>
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T08:23:30+00:00</t>
+          <t>2026-06-08T14:41:06+00:00</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>159</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -11104,11 +11104,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -11156,15 +11156,15 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>AD COMMODITIES PTY LTD</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr"/>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>A A COMPANY PTY LTD</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>chosen-sprite@2x.png</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr"/>
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11174,15 +11174,15 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>ALC Trading PTY LTD</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr"/>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>A A COMPANY PTY LTD</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>reception@aaco.com.au</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11192,7 +11192,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>ALKAWTHER TRADING PTY LTD</t>
+          <t>AD COMMODITIES PTY LTD</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>AMPCO MEAT GROUP PTY LTD</t>
+          <t>ALC Trading PTY LTD</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr"/>
@@ -11228,7 +11228,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>AO YIN PTY LTD</t>
+          <t>ALKAWTHER TRADING PTY LTD</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr"/>
@@ -11246,7 +11246,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>AP Link Trading Pty Ltd</t>
+          <t>AMPCO MEAT GROUP PTY LTD</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
@@ -11264,7 +11264,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+          <t>AO YIN PTY LTD</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
@@ -11282,7 +11282,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>AUSTRALIAN MEAT GROUP</t>
+          <t>AP Link Trading Pty Ltd</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
@@ -11300,7 +11300,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>AUSVISION MEAT PROCESSORS PTY LTD T/A BEAUFORT RIVER MEATS</t>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr"/>
@@ -11318,15 +11318,15 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Agricomm Trading Australia</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>acclivestock@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11336,15 +11336,15 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Amulet International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>akropp@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11354,15 +11354,15 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Amulet International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>020 100000</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>b_dale@westnet.com.au</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11372,15 +11372,15 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Andrews Meat Industries Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>bpweighbridge@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11390,15 +11390,15 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Ausfine Foods International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr"/>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>btaylor@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11408,15 +11408,15 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Ausgraze Exports PTY LTD</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr"/>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>bvalley@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11426,15 +11426,15 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Austral Pacific Exports Pty. Ltd.</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>dbailey@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11444,15 +11444,15 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Australasian Casing Co Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>dfstock@bigpond.com</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11462,15 +11462,15 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Australia Food Trading Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>gkeane@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11480,15 +11480,15 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Australian Beef Group</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr"/>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>hevans@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11498,15 +11498,15 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Australian Beef Trading Centre Pty Ltd trade as Synergy Industry Group</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>jtitmarsh@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11516,15 +11516,15 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Australian Organic Meat</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr"/>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>katecraft@bigpond.com</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11534,15 +11534,15 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>B &amp; G EXPORT CORPORATION PTY LTD</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr"/>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>khflack@bigpond.com</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11552,15 +11552,15 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>B &amp; H Global Foods Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr"/>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>kmcgrane@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11570,15 +11570,15 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>B B Products (Australia) P/L</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr"/>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>mhoward@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11588,15 +11588,15 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>BINDAREE BEEF GROUP</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr"/>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>michael.barron@bigpond.com</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11606,15 +11606,15 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>BRAU Enterprises Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr"/>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>mnorton@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11624,15 +11624,15 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Borthwick Foods Retail Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr"/>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>myates@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11642,15 +11642,15 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Bounty Foods International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr"/>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>ocwbridge@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11660,15 +11660,15 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Bridge Procurement &amp; Services Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr"/>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>pferguson@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11678,15 +11678,15 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Bullys Beef Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr"/>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>reception@accbeef.net.au</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11696,15 +11696,15 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>C.M. Company PTY ltd</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr"/>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>tom.wdcattle@gmail.com</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11714,15 +11714,15 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>CHOICE M PTY LTD</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSTRALIAN COUNTRY CHOICE PTY LTD</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>trevorfrancis@live.com.au</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11732,7 +11732,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>CRAIG MOSTYN &amp; CO PTY LTD</t>
+          <t>AUSTRALIAN MEAT GROUP</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>CROWN STATE PASTORAL COMPANY PTY LTD</t>
+          <t>AUSVISION MEAT PROCESSORS PTY LTD T/A BEAUFORT RIVER MEATS</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr"/>
@@ -11768,15 +11768,15 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Cadopen Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr"/>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSVISION MEAT PROCESSORS PTY LTD T/A BEAUFORT RIVER MEATS</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Brm.LivestockGrid@brmeats.com.au</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11786,15 +11786,15 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Cedar Meats (Aust) Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr"/>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSVISION MEAT PROCESSORS PTY LTD T/A BEAUFORT RIVER MEATS</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>amp.office@brmeats.com.au</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11804,15 +11804,15 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Central Agri Group Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr"/>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSVISION MEAT PROCESSORS PTY LTD T/A BEAUFORT RIVER MEATS</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>brm.admin@brmeats.com.au</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11822,15 +11822,15 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Clover Valley Meat Company Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr"/>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>AUSVISION MEAT PROCESSORS PTY LTD T/A BEAUFORT RIVER MEATS</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>n.nanda@liveships.com.au</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11840,7 +11840,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Consolidated Foodco</t>
+          <t>Agricomm Trading Australia</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr"/>
@@ -11858,7 +11858,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Cory Johnston Australia Pty. Ltd.</t>
+          <t>Amulet International Pty Ltd</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr"/>
@@ -11876,13 +11876,13 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Dorper Lamb Pty Ltd</t>
+          <t>Amulet International Pty Ltd</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr"/>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
+          <t>020 100000</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Down Under Prestige Meat Co. Pty Ltd</t>
+          <t>Andrews Meat Industries Pty Ltd</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr"/>
@@ -11912,15 +11912,15 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>FETTAYLEH WHOLESALE MEAT SUPPLY PTY LTD</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr"/>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>18d2f96d279149989b95faf0a4b41882@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11930,15 +11930,15 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>FLAVOUR MAKERS</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr"/>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>2062d0a4929b45348643784b5cb39c36@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11948,15 +11948,15 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr"/>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>271e9fa3230b4eec94b02bf95780f5f2@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11966,15 +11966,15 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>FORESIGHT FOODS AUSTRALIA PTY LTD</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr"/>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>460ff4620fa44cba8df530afde949785@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -11984,15 +11984,15 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Fayman International PTY LTD</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr"/>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>5d1795a2db124a268f1e1bd88f503500@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12002,15 +12002,15 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Foodworks International PTY LTD</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr"/>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12020,15 +12020,15 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Friends of Meat Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr"/>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>79baaa8e09c746d2b7401643b99792e0@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12038,15 +12038,15 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>G &amp; K O'CONNOR PTY LTD</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr"/>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>8eb368c655b84e029ed79ad7a5c1718e@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12056,15 +12056,15 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>GREENHAM TASMANIA PTY LTD</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr"/>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>9a65e97ebe8141fca0c4fd686f70996b@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12074,15 +12074,15 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Garlo's Pies</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr"/>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>ed436f5053144538958ad06a5005e99a@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12092,15 +12092,15 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Garra International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr"/>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Andrews Meat Industries Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>sales@andrewsmeat.com</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12110,7 +12110,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Global Meats Pty Ltd</t>
+          <t>Ausfine Foods International Pty Ltd</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr"/>
@@ -12128,15 +12128,15 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Good Food Exports (Australia)</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr"/>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Ausfine Foods International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>sales@ausfine.com</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12146,15 +12146,15 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Greenham Gippsland Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr"/>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Ausfine Foods International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>salesindo@ausfine.com</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12164,7 +12164,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>H.R.Woodward Foods Australia</t>
+          <t>Ausgraze Exports PTY LTD</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>H.R.Woodward Foods Australia</t>
+          <t>Austral Pacific Exports Pty. Ltd.</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr"/>
@@ -12200,7 +12200,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>HARVEY BEEF</t>
+          <t>Australasian Casing Co Pty Ltd</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr"/>
@@ -12218,7 +12218,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>HILAL MEAT PRODUCTS CO PTY LTD.</t>
+          <t>Australia Food Trading Pty Ltd</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr"/>
@@ -12236,7 +12236,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>HOMEBUSH EXPORT MEAT CO PTY LTD</t>
+          <t>Australian Beef Group</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Haywill Holdings Pty Ltd</t>
+          <t>Australian Beef Trading Centre Pty Ltd trade as Synergy Industry Group</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr"/>
@@ -12272,7 +12272,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Hewitt Foods</t>
+          <t>Australian Organic Meat</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr"/>
@@ -12290,15 +12290,15 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Hokubee Australia</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr"/>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Australian Organic Meat</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>admin@aomgroup.com.au</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12308,15 +12308,15 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>INTER AGRI GROUP PTY LTD</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr"/>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Australian Organic Meat</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>matt@aomgroup.com.au</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12326,15 +12326,15 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Ineffable Distribution Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr"/>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Australian Organic Meat</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>simone@aomgroup.com.au</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12344,15 +12344,15 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Integrated Meat Solutions pty Ltd</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr"/>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Australian Organic Meat</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12362,7 +12362,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>JBS AUSTRALIA PTY LTD</t>
+          <t>B &amp; G EXPORT CORPORATION PTY LTD</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr"/>
@@ -12380,15 +12380,15 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>JOC Australia Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr"/>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>B &amp; G EXPORT CORPORATION PTY LTD</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>admin@bandg.com.au</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12398,15 +12398,15 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>JOYCE'S TRADING PTY LIMITED</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr"/>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>B &amp; G EXPORT CORPORATION PTY LTD</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>sales@bandg.com.au</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12416,7 +12416,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>JR EXPORTS PTY LTD</t>
+          <t>B &amp; H Global Foods Pty Ltd</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr"/>
@@ -12434,15 +12434,15 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>John Dee (Export) Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr"/>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>B &amp; H Global Foods Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>memari@bhge.com.au</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12452,15 +12452,15 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>KC Natural Pty Limited</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr"/>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>B &amp; H Global Foods Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>sales@bhge.com.au</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12470,7 +12470,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Keystone Australia</t>
+          <t>B B Products (Australia) P/L</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr"/>
@@ -12488,15 +12488,15 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Kimberley Meat Company</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr"/>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>B B Products (Australia) P/L</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>info@bbproducts.com.au</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12506,15 +12506,15 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>King River Ag Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr"/>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>B B Products (Australia) P/L</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12524,7 +12524,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>LANGREY INTERNATIONAL PTY LTD</t>
+          <t>BINDAREE BEEF GROUP</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
@@ -12542,7 +12542,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>LOTTE INTERNATIONAL OCEANIA PTY LTD</t>
+          <t>BRAU Enterprises Pty Ltd</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr"/>
@@ -12560,7 +12560,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Lanexco Australia Pty Ltd</t>
+          <t>Borthwick Foods Retail Pty Ltd</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
@@ -12578,15 +12578,15 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Langley Trading Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Borthwick Foods Retail Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>borthwickfoods@borthwickfoods.com.au</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12596,7 +12596,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Luttick Australia Pty Ltd</t>
+          <t>Bounty Foods International Pty Ltd</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr"/>
@@ -12614,15 +12614,15 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>M.C. HERD PTY LTD</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr"/>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Bounty Foods International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Paul@BountyFoods.com.au</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12632,15 +12632,15 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>MEATOO INTERNATIONAL GROUP IMP &amp; EXP PTY LTD</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr"/>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Bounty Foods International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Peter@BountyFoods.com.au</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12650,15 +12650,15 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>MORT &amp; CO LTD</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr"/>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Bounty Foods International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>u003ePaul@BountyFoods.com.au</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12668,7 +12668,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>MT Food Group</t>
+          <t>Bridge Procurement &amp; Services Pty Ltd</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr"/>
@@ -12686,7 +12686,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Malin International Trading Company</t>
+          <t>Bullys Beef Pty Ltd</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr"/>
@@ -12704,7 +12704,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Mandel Trading Pty Ltd</t>
+          <t>C.M. Company PTY ltd</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr"/>
@@ -12722,7 +12722,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Mandeville Meat Group Pty Ltd</t>
+          <t>CHOICE M PTY LTD</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Margaret River Premium Meat Exports</t>
+          <t>CRAIG MOSTYN &amp; CO PTY LTD</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr"/>
@@ -12758,15 +12758,15 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Mathias Australia Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr"/>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>CRAIG MOSTYN &amp; CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>6073Contactcmostyn@craigmostyn.com.au</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12776,15 +12776,15 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Matrad Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr"/>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>CRAIG MOSTYN &amp; CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>6959Contactcmostyn@craigmostyn.com.au</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12794,15 +12794,15 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>McPhee Bros Exports Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr"/>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>CRAIG MOSTYN &amp; CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>cmostyn@craigmostyn.com.au</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12812,7 +12812,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Midfield Commodities Pty Ltd</t>
+          <t>CROWN STATE PASTORAL COMPANY PTY LTD</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr"/>
@@ -12830,15 +12830,15 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Midfield Meat International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr"/>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>CROWN STATE PASTORAL COMPANY PTY LTD</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>enquiries@crownstate.com.au</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12848,15 +12848,15 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Mitsui &amp; Co. (Australia) LTD.</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr"/>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>CROWN STATE PASTORAL COMPANY PTY LTD</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12866,7 +12866,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Mulwarra Export</t>
+          <t>Cadopen Pty Ltd</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr"/>
@@ -12884,7 +12884,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>NCMC Foods Pty Ltd</t>
+          <t>Cedar Meats (Aust) Pty Ltd</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr"/>
@@ -12902,15 +12902,15 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>NCMC Foods Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr"/>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Cedar Meats (Aust) Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>enquiries@cedarmeats.com</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12920,15 +12920,15 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>NH Foods Australia Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr"/>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Cedar Meats (Aust) Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>info@cedarmeats.com</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12938,7 +12938,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Naturally Australian Meat &amp; Game Pty Ltd</t>
+          <t>Central Agri Group Pty Ltd</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr"/>
@@ -12956,15 +12956,15 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>New England Exports Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr"/>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Central Agri Group Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>info@centralagrigroup.com.au</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -12974,7 +12974,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>New World Foods</t>
+          <t>Clover Valley Meat Company Pty Ltd</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr"/>
@@ -12992,15 +12992,15 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Nowaco Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Clover Valley Meat Company Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>clayton@clovervalley.com.au</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13010,15 +13010,15 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>OBE Beef Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Clover Valley Meat Company Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13028,7 +13028,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>OMC AUSTRALIA PTY LTD</t>
+          <t>Consolidated Foodco</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Oasis Exports Pty. Ltd.</t>
+          <t>Cory Johnston Australia Pty. Ltd.</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
@@ -13064,15 +13064,15 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Oz Nature Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr"/>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Cory Johnston Australia Pty. Ltd.</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>info@coryjohnston.com.au</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13082,15 +13082,15 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>PASTORAL INDUSTRIES PTY LTD</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr"/>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Cory Johnston Australia Pty. Ltd.</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13100,7 +13100,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>PRESTIGE FOODS INT P/L</t>
+          <t>Dorper Lamb Pty Ltd</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr"/>
@@ -13118,15 +13118,15 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Pacific Ocean Enterprises pty ltd</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr"/>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Dorper Lamb Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>dale@dorperlamb.com.au</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13136,15 +13136,15 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Paradigm Foods Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Dorper Lamb Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>graeme@dorperlamb.com.au</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13154,15 +13154,15 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Positive Proteins</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr"/>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Dorper Lamb Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>sales@dorperlamb.com.au</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13172,7 +13172,7 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Providore Global Pty Ltd</t>
+          <t>Down Under Prestige Meat Co. Pty Ltd</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Q &amp; B Trading Pty Ltd</t>
+          <t>FETTAYLEH WHOLESALE MEAT SUPPLY PTY LTD</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr"/>
@@ -13208,15 +13208,15 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>RAMSDEN AGRICULTURE</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr"/>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FETTAYLEH WHOLESALE MEAT SUPPLY PTY LTD</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>info@fettayleh.com</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13226,7 +13226,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>RANGERS VALLEY CATTLE STATION PTY LTD</t>
+          <t>FLAVOUR MAKERS</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr"/>
@@ -13244,15 +13244,15 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>RTC Foods PTY Limited</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr"/>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLAVOUR MAKERS</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Flavour_Makers_BMS_Horiz_Pos_RGB_1_1_d95cecd9-4c36-4f68-8ff7-3bab80b45a08_200x@2x.png</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13262,15 +13262,15 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Ralphs Meat Company Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr"/>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLAVOUR MAKERS</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>info@flavourmakers.com.au</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13280,7 +13280,7 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Rashad Aziz Investments</t>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr"/>
@@ -13298,15 +13298,15 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>Ravensworth Agricultural Company of Australia</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr"/>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>FIEUSA@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13316,15 +13316,15 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Remesis Group Pty Limited</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr"/>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Livestock@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13334,15 +13334,15 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Roaring Forties Farms</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr"/>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Skinsnwool@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13352,15 +13352,15 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Robran International Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr"/>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>WAStock@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13370,15 +13370,15 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Ryan Meat Company Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr"/>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>acpay@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13388,15 +13388,15 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>SIGNIFY PTY LIMITED</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr"/>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>fletcherindia@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13406,15 +13406,15 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>SK Rabi International Pty Ltd trading as SKRI</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="inlineStr"/>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>grainsales@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13424,15 +13424,15 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>SORBY ADAMS TRADING CO PTY LTD</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr"/>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>logistics@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13442,15 +13442,15 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>SOUTH AUSTRALIAN CATTLE CO PTY LTD</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr"/>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>mailbox@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13460,15 +13460,15 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>STELLA FOODS AUSTRALIA PTY LTD</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr"/>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>receipts@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13478,15 +13478,15 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Saltbush Livestock Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr"/>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>sales@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13496,15 +13496,15 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Samex Australian Meat Co Pty L</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr"/>
-      <c r="C133" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>FLETCHER INTERNATIONAL EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>uksales@fletchint.com.au</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13514,7 +13514,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Security Foods Exports Pty Ltd</t>
+          <t>FORESIGHT FOODS AUSTRALIA PTY LTD</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr"/>
@@ -13532,7 +13532,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Signature Beef Pty Ltd</t>
+          <t>Fayman International PTY LTD</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr"/>
@@ -13550,7 +13550,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Silverfield Enterprises</t>
+          <t>Foodworks International PTY LTD</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr"/>
@@ -13568,7 +13568,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Simplot Australia Pty ltd</t>
+          <t>Friends of Meat Pty Ltd</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr"/>
@@ -13586,15 +13586,15 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Southland (Australia) Pty Limited</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr"/>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Friends of Meat Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>ajax-loader@2x.gif</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13604,7 +13604,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Stockyard Beef Pty Ltd</t>
+          <t>G &amp; K O'CONNOR PTY LTD</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Subast Pty Ltd</t>
+          <t>GREENHAM TASMANIA PTY LTD</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr"/>
@@ -13640,15 +13640,15 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Swift &amp; Company Trade Group</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr"/>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>GREENHAM TASMANIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>sales@greenham.com.au</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13658,7 +13658,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>THE TRUSTEE FOR JFW ENTERPRISES TRUST</t>
+          <t>Garlo's Pies</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr"/>
@@ -13676,15 +13676,15 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>TOP CUT FOOD INDUSTRIES PTY LTD</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Garlo's Pies</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>headoffice@garlospies.com.au</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13694,7 +13694,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Tasmanian Quality Meats</t>
+          <t>Garra International Pty Ltd</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr"/>
@@ -13712,7 +13712,7 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Teys Australia Pty Ltd</t>
+          <t>Global Meats Pty Ltd</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr"/>
@@ -13730,7 +13730,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>The Game Meats Company</t>
+          <t>Good Food Exports (Australia)</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr"/>
@@ -13748,15 +13748,15 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>Therfield Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B147" s="7" t="inlineStr"/>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Good Food Exports (Australia)</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>sales@goodfoodexports.com.au</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13766,7 +13766,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>Tradevine</t>
+          <t>Greenham Gippsland Pty Ltd</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr"/>
@@ -13784,7 +13784,7 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>Two Rivers Agri Group Pty Ltd</t>
+          <t>H.R.Woodward Foods Australia</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
@@ -13802,7 +13802,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>United World Enterprises Pty Ltd</t>
+          <t>H.R.Woodward Foods Australia</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr"/>
@@ -13820,7 +13820,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>VG Food Pty Ltd</t>
+          <t>HARVEY BEEF</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr"/>
@@ -13838,15 +13838,15 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>W&amp;B Holdings Corporation PTY LTD</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr"/>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>HARVEY BEEF</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>info@harvestroad.com</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13856,7 +13856,7 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>WA Meat Exports</t>
+          <t>HILAL MEAT PRODUCTS CO PTY LTD.</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr"/>
@@ -13874,15 +13874,15 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>WARMOLL FOODS PTY LTD</t>
-        </is>
-      </c>
-      <c r="B154" s="7" t="inlineStr"/>
-      <c r="C154" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>HILAL MEAT PRODUCTS CO PTY LTD.</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>contact@dabbaghgroup.com.au</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13892,15 +13892,15 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr"/>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>HILAL MEAT PRODUCTS CO PTY LTD.</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>info@dabbaghgroup.com.au</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13910,7 +13910,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>WHITE STRIPE FOODS PTY LTD</t>
+          <t>HOMEBUSH EXPORT MEAT CO PTY LTD</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr"/>
@@ -13928,15 +13928,15 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>WYLOO PASTORAL COMPANY PTY LTD</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr"/>
-      <c r="C157" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>HOMEBUSH EXPORT MEAT CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>admin@hem.com.au</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13946,7 +13946,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>Wingham Beef Exports Pty Ltd</t>
+          <t>Haywill Holdings Pty Ltd</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr"/>
@@ -13964,15 +13964,15 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>World Wide Exporters Pty Ltd</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr"/>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>+61 02 9463 9333 1800 023 100</t>
-        </is>
-      </c>
+          <t>Haywill Holdings Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
@@ -13982,23 +13982,4091 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
+          <t>Haywill Holdings Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>sales@haywill.com.au</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr"/>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>Haywill Holdings Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>sales@haywill.comau</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr"/>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>Hewitt Foods</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr"/>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>Hokubee Australia</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr"/>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>Hokubee Australia</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>joel.laurie@hokubee.com.au</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr"/>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>Hokubee Australia</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr"/>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>INTER AGRI GROUP PTY LTD</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr"/>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>INTER AGRI GROUP PTY LTD</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>adrian@interagri.com.au</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr"/>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>INTER AGRI GROUP PTY LTD</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>sales@interagri.com.au</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr"/>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>INTER AGRI GROUP PTY LTD</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>simon@interagri.com.au</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr"/>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>Ineffable Distribution Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr"/>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Integrated Meat Solutions pty Ltd</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr"/>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>Integrated Meat Solutions pty Ltd</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>michelle@integratedmeatsolutions.com.au</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr"/>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>JBS AUSTRALIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr"/>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>JBS AUSTRALIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>communications@jbssa.com.au</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr"/>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>JOC Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr"/>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>JOC Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>corp@jocaustralia.com</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr"/>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>JOYCE'S TRADING PTY LIMITED</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr"/>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>JR EXPORTS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr"/>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>John Dee (Export) Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr"/>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr"/>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr"/>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>79baaa8e09c746d2b7401643b99792e0@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr"/>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>8c4075d5481d476e945486754f783364@sentry.io</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr"/>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>8eb368c655b84e029ed79ad7a5c1718e@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr"/>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>9a65e97ebe8141fca0c4fd686f70996b@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr"/>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>accounts@kennyscreek.com.au</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr"/>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>kc@kennyscreek.com.au</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr"/>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>sam@kennyscreek.com.au</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr"/>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>KC Natural Pty Limited</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>willzheng@kennyscreek.com.au</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr"/>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>Keystone Australia</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr"/>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>Kimberley Meat Company</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr"/>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>King River Ag Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr"/>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>King River Ag Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>contact@digitaloneagency.com.au</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr"/>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>King River Ag Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>info@kingriver.com.au</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr"/>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>LANGREY INTERNATIONAL PTY LTD</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr"/>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>LOTTE INTERNATIONAL OCEANIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr"/>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>LOTTE INTERNATIONAL OCEANIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>lotteir@lotte.net</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr"/>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>Lanexco Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr"/>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>Lanexco Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>steve@lanexco.co.nz</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr"/>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>Lanexco Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr"/>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>Langley Trading Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr"/>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>Luttick Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr"/>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>M.C. HERD PTY LTD</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr"/>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>MEATOO INTERNATIONAL GROUP IMP &amp; EXP PTY LTD</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr"/>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr"/>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>admin@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr"/>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>fert.sales@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr"/>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>grassdale.admin@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr"/>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>pinegrove.admin@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr"/>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>servicecentre@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr"/>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>transport@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="inlineStr"/>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>MORT &amp; CO LTD</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>yarranbrook.feedlot@mortco.com.au</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr"/>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>MT Food Group</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr"/>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>MT Food Group</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>sales@mtfoodgroup.com.au</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr"/>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>Malin International Trading Company</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr"/>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>Mandel Trading Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr"/>
+      <c r="C216" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>Mandeville Meat Group Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr"/>
+      <c r="C217" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t>Margaret River Premium Meat Exports</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr"/>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>Margaret River Premium Meat Exports</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>enquiries@stoneaxepastoral.com.au</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr"/>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>Margaret River Premium Meat Exports</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr"/>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>Mathias Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr"/>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>Mathias Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>info@farmlandsmathias.com</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr"/>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>Matrad Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr"/>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>McPhee Bros Exports Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr"/>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr"/>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>adrianmcnicol@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr"/>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>cchantrell@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr"/>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>cchantrll@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="inlineStr"/>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>hello@themenectar.com</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr"/>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>jason@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr"/>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>jferguson@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr"/>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>midfield@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr"/>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>nathan@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="inlineStr"/>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Commodities Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>nickfuss@midcom.com.au</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr"/>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Meat International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr"/>
+      <c r="C235" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D235" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Meat International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>marketing@midfield.com.au</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr"/>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>Midfield Meat International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>media@midfield.com.au</t>
+        </is>
+      </c>
+      <c r="C237" s="7" t="inlineStr"/>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>Mitsui &amp; Co. (Australia) LTD.</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr"/>
+      <c r="C238" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>Mulwarra Export</t>
+        </is>
+      </c>
+      <c r="B239" s="7" t="inlineStr"/>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>Mulwarra Export</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>mulwarra@mulwarra.com.au</t>
+        </is>
+      </c>
+      <c r="C240" s="7" t="inlineStr"/>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>NCMC Foods Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B241" s="7" t="inlineStr"/>
+      <c r="C241" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D241" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="7" t="inlineStr">
+        <is>
+          <t>NCMC Foods Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B242" s="7" t="inlineStr"/>
+      <c r="C242" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="7" t="inlineStr">
+        <is>
+          <t>NH Foods Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B243" s="7" t="inlineStr"/>
+      <c r="C243" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D243" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>Naturally Australian Meat &amp; Game Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B244" s="7" t="inlineStr"/>
+      <c r="C244" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="7" t="inlineStr">
+        <is>
+          <t>Naturally Australian Meat &amp; Game Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B245" s="7" t="inlineStr">
+        <is>
+          <t>admin@namag.com.au</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="inlineStr"/>
+      <c r="D245" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="inlineStr">
+        <is>
+          <t>New England Exports Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="inlineStr"/>
+      <c r="C246" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="7" t="inlineStr">
+        <is>
+          <t>New England Exports Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B247" s="7" t="inlineStr">
+        <is>
+          <t>info@threecreekbeef.com</t>
+        </is>
+      </c>
+      <c r="C247" s="7" t="inlineStr"/>
+      <c r="D247" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="7" t="inlineStr">
+        <is>
+          <t>New World Foods</t>
+        </is>
+      </c>
+      <c r="B248" s="7" t="inlineStr"/>
+      <c r="C248" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B249" s="7" t="inlineStr"/>
+      <c r="C249" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B250" s="7" t="inlineStr">
+        <is>
+          <t>dda@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C250" s="7" t="inlineStr"/>
+      <c r="D250" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B251" s="7" t="inlineStr">
+        <is>
+          <t>dst@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C251" s="7" t="inlineStr"/>
+      <c r="D251" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>ena@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="inlineStr"/>
+      <c r="D252" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>hsb@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C253" s="7" t="inlineStr"/>
+      <c r="D253" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>jhb@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C254" s="7" t="inlineStr"/>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B255" s="7" t="inlineStr">
+        <is>
+          <t>khb@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C255" s="7" t="inlineStr"/>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>ldg@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C256" s="7" t="inlineStr"/>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B257" s="7" t="inlineStr">
+        <is>
+          <t>mala@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C257" s="7" t="inlineStr"/>
+      <c r="D257" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B258" s="7" t="inlineStr">
+        <is>
+          <t>mbh@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C258" s="7" t="inlineStr"/>
+      <c r="D258" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B259" s="7" t="inlineStr">
+        <is>
+          <t>mikc@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C259" s="7" t="inlineStr"/>
+      <c r="D259" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>msk@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C260" s="7" t="inlineStr"/>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B261" s="7" t="inlineStr">
+        <is>
+          <t>sas@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C261" s="7" t="inlineStr"/>
+      <c r="D261" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="7" t="inlineStr">
+        <is>
+          <t>Nowaco Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>zhan@nowaco.com</t>
+        </is>
+      </c>
+      <c r="C262" s="7" t="inlineStr"/>
+      <c r="D262" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t>OBE Beef Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B263" s="7" t="inlineStr"/>
+      <c r="C263" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D263" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="7" t="inlineStr">
+        <is>
+          <t>OMC AUSTRALIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr"/>
+      <c r="C264" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="7" t="inlineStr">
+        <is>
+          <t>OMC AUSTRALIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B265" s="7" t="inlineStr">
+        <is>
+          <t>enquiries@oakdalemeat.com.au</t>
+        </is>
+      </c>
+      <c r="C265" s="7" t="inlineStr"/>
+      <c r="D265" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="inlineStr">
+        <is>
+          <t>Oasis Exports Pty. Ltd.</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr"/>
+      <c r="C266" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D266" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="7" t="inlineStr">
+        <is>
+          <t>Oz Nature Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B267" s="7" t="inlineStr"/>
+      <c r="C267" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D267" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="7" t="inlineStr">
+        <is>
+          <t>PASTORAL INDUSTRIES PTY LTD</t>
+        </is>
+      </c>
+      <c r="B268" s="7" t="inlineStr"/>
+      <c r="C268" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="7" t="inlineStr">
+        <is>
+          <t>PRESTIGE FOODS INT P/L</t>
+        </is>
+      </c>
+      <c r="B269" s="7" t="inlineStr"/>
+      <c r="C269" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D269" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="inlineStr">
+        <is>
+          <t>PRESTIGE FOODS INT P/L</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>PFI_Logo_2025_landscape_1_x80@2x.png</t>
+        </is>
+      </c>
+      <c r="C270" s="7" t="inlineStr"/>
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="7" t="inlineStr">
+        <is>
+          <t>PRESTIGE FOODS INT P/L</t>
+        </is>
+      </c>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>pfi@prestigefoods.com.au</t>
+        </is>
+      </c>
+      <c r="C271" s="7" t="inlineStr"/>
+      <c r="D271" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="7" t="inlineStr">
+        <is>
+          <t>Pacific Ocean Enterprises pty ltd</t>
+        </is>
+      </c>
+      <c r="B272" s="7" t="inlineStr"/>
+      <c r="C272" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D272" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="7" t="inlineStr">
+        <is>
+          <t>Paradigm Foods Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B273" s="7" t="inlineStr"/>
+      <c r="C273" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="7" t="inlineStr">
+        <is>
+          <t>Positive Proteins</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr"/>
+      <c r="C274" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="7" t="inlineStr">
+        <is>
+          <t>Providore Global Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr"/>
+      <c r="C275" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D275" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>Providore Global Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>sales@providoreglobal.com</t>
+        </is>
+      </c>
+      <c r="C276" s="7" t="inlineStr"/>
+      <c r="D276" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="7" t="inlineStr">
+        <is>
+          <t>Providore Global Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>tallawanta@providoreglobal.com</t>
+        </is>
+      </c>
+      <c r="C277" s="7" t="inlineStr"/>
+      <c r="D277" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="7" t="inlineStr">
+        <is>
+          <t>Q &amp; B Trading Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr"/>
+      <c r="C278" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D278" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>RAMSDEN AGRICULTURE</t>
+        </is>
+      </c>
+      <c r="B279" s="7" t="inlineStr"/>
+      <c r="C279" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D279" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>RANGERS VALLEY CATTLE STATION PTY LTD</t>
+        </is>
+      </c>
+      <c r="B280" s="7" t="inlineStr"/>
+      <c r="C280" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D280" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="7" t="inlineStr">
+        <is>
+          <t>RANGERS VALLEY CATTLE STATION PTY LTD</t>
+        </is>
+      </c>
+      <c r="B281" s="7" t="inlineStr">
+        <is>
+          <t>user@domain.com</t>
+        </is>
+      </c>
+      <c r="C281" s="7" t="inlineStr"/>
+      <c r="D281" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>RTC Foods PTY Limited</t>
+        </is>
+      </c>
+      <c r="B282" s="7" t="inlineStr"/>
+      <c r="C282" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D282" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="7" t="inlineStr">
+        <is>
+          <t>Ralphs Meat Company Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B283" s="7" t="inlineStr"/>
+      <c r="C283" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D283" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="7" t="inlineStr">
+        <is>
+          <t>Rashad Aziz Investments</t>
+        </is>
+      </c>
+      <c r="B284" s="7" t="inlineStr"/>
+      <c r="C284" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D284" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>Ravensworth Agricultural Company of Australia</t>
+        </is>
+      </c>
+      <c r="B285" s="7" t="inlineStr"/>
+      <c r="C285" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D285" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="7" t="inlineStr">
+        <is>
+          <t>Ravensworth Agricultural Company of Australia</t>
+        </is>
+      </c>
+      <c r="B286" s="7" t="inlineStr">
+        <is>
+          <t>18d2f96d279149989b95faf0a4b41882@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C286" s="7" t="inlineStr"/>
+      <c r="D286" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="7" t="inlineStr">
+        <is>
+          <t>Ravensworth Agricultural Company of Australia</t>
+        </is>
+      </c>
+      <c r="B287" s="7" t="inlineStr">
+        <is>
+          <t>2062d0a4929b45348643784b5cb39c36@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C287" s="7" t="inlineStr"/>
+      <c r="D287" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="7" t="inlineStr">
+        <is>
+          <t>Ravensworth Agricultural Company of Australia</t>
+        </is>
+      </c>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>5d1795a2db124a268f1e1bd88f503500@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C288" s="7" t="inlineStr"/>
+      <c r="D288" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="inlineStr">
+        <is>
+          <t>Ravensworth Agricultural Company of Australia</t>
+        </is>
+      </c>
+      <c r="B289" s="7" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C289" s="7" t="inlineStr"/>
+      <c r="D289" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="7" t="inlineStr">
+        <is>
+          <t>Ravensworth Agricultural Company of Australia</t>
+        </is>
+      </c>
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>example@mysite.com</t>
+        </is>
+      </c>
+      <c r="C290" s="7" t="inlineStr"/>
+      <c r="D290" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>Remesis Group Pty Limited</t>
+        </is>
+      </c>
+      <c r="B291" s="7" t="inlineStr"/>
+      <c r="C291" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>Roaring Forties Farms</t>
+        </is>
+      </c>
+      <c r="B292" s="7" t="inlineStr"/>
+      <c r="C292" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="7" t="inlineStr">
+        <is>
+          <t>Roaring Forties Farms</t>
+        </is>
+      </c>
+      <c r="B293" s="7" t="inlineStr">
+        <is>
+          <t>info@roaringfortiesfarms.com.au</t>
+        </is>
+      </c>
+      <c r="C293" s="7" t="inlineStr"/>
+      <c r="D293" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t>Robran International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B294" s="7" t="inlineStr"/>
+      <c r="C294" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D294" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="inlineStr">
+        <is>
+          <t>Robran International Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B295" s="7" t="inlineStr">
+        <is>
+          <t>trade@robran.com.au</t>
+        </is>
+      </c>
+      <c r="C295" s="7" t="inlineStr"/>
+      <c r="D295" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="7" t="inlineStr">
+        <is>
+          <t>Ryan Meat Company Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B296" s="7" t="inlineStr"/>
+      <c r="C296" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D296" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="7" t="inlineStr">
+        <is>
+          <t>Ryan Meat Company Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B297" s="7" t="inlineStr">
+        <is>
+          <t>admin@ryanmc.com.au</t>
+        </is>
+      </c>
+      <c r="C297" s="7" t="inlineStr"/>
+      <c r="D297" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="7" t="inlineStr">
+        <is>
+          <t>SIGNIFY PTY LIMITED</t>
+        </is>
+      </c>
+      <c r="B298" s="7" t="inlineStr"/>
+      <c r="C298" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D298" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="7" t="inlineStr">
+        <is>
+          <t>SIGNIFY PTY LIMITED</t>
+        </is>
+      </c>
+      <c r="B299" s="7" t="inlineStr">
+        <is>
+          <t>info@signify.com.au</t>
+        </is>
+      </c>
+      <c r="C299" s="7" t="inlineStr"/>
+      <c r="D299" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="7" t="inlineStr">
+        <is>
+          <t>SIGNIFY PTY LIMITED</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>john@signify.com.au</t>
+        </is>
+      </c>
+      <c r="C300" s="7" t="inlineStr"/>
+      <c r="D300" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="7" t="inlineStr">
+        <is>
+          <t>SIGNIFY PTY LIMITED</t>
+        </is>
+      </c>
+      <c r="B301" s="7" t="inlineStr">
+        <is>
+          <t>min@signify.com.au</t>
+        </is>
+      </c>
+      <c r="C301" s="7" t="inlineStr"/>
+      <c r="D301" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="7" t="inlineStr">
+        <is>
+          <t>SIGNIFY PTY LIMITED</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>sharyn@signify.com.au</t>
+        </is>
+      </c>
+      <c r="C302" s="7" t="inlineStr"/>
+      <c r="D302" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="7" t="inlineStr">
+        <is>
+          <t>SK Rabi International Pty Ltd trading as SKRI</t>
+        </is>
+      </c>
+      <c r="B303" s="7" t="inlineStr"/>
+      <c r="C303" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D303" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="inlineStr">
+        <is>
+          <t>SK Rabi International Pty Ltd trading as SKRI</t>
+        </is>
+      </c>
+      <c r="B304" s="7" t="inlineStr">
+        <is>
+          <t>operations@skri.com.au</t>
+        </is>
+      </c>
+      <c r="C304" s="7" t="inlineStr"/>
+      <c r="D304" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>SORBY ADAMS TRADING CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B305" s="7" t="inlineStr"/>
+      <c r="C305" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D305" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="7" t="inlineStr">
+        <is>
+          <t>SORBY ADAMS TRADING CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B306" s="7" t="inlineStr">
+        <is>
+          <t>digby@sorbyadamswines.com</t>
+        </is>
+      </c>
+      <c r="C306" s="7" t="inlineStr"/>
+      <c r="D306" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="7" t="inlineStr">
+        <is>
+          <t>SORBY ADAMS TRADING CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B307" s="7" t="inlineStr">
+        <is>
+          <t>info@sorbyadamswines.com</t>
+        </is>
+      </c>
+      <c r="C307" s="7" t="inlineStr"/>
+      <c r="D307" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="7" t="inlineStr">
+        <is>
+          <t>SORBY ADAMS TRADING CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B308" s="7" t="inlineStr">
+        <is>
+          <t>mel@sorbyadamswines.com</t>
+        </is>
+      </c>
+      <c r="C308" s="7" t="inlineStr"/>
+      <c r="D308" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="7" t="inlineStr">
+        <is>
+          <t>SORBY ADAMS TRADING CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B309" s="7" t="inlineStr">
+        <is>
+          <t>simon@sorbyadamswines.com</t>
+        </is>
+      </c>
+      <c r="C309" s="7" t="inlineStr"/>
+      <c r="D309" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="7" t="inlineStr">
+        <is>
+          <t>SOUTH AUSTRALIAN CATTLE CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B310" s="7" t="inlineStr"/>
+      <c r="C310" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D310" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>SOUTH AUSTRALIAN CATTLE CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B311" s="7" t="inlineStr">
+        <is>
+          <t>beef@kandq.com.au</t>
+        </is>
+      </c>
+      <c r="C311" s="7" t="inlineStr"/>
+      <c r="D311" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="7" t="inlineStr">
+        <is>
+          <t>SOUTH AUSTRALIAN CATTLE CO PTY LTD</t>
+        </is>
+      </c>
+      <c r="B312" s="7" t="inlineStr">
+        <is>
+          <t>example@email.com</t>
+        </is>
+      </c>
+      <c r="C312" s="7" t="inlineStr"/>
+      <c r="D312" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="7" t="inlineStr">
+        <is>
+          <t>STELLA FOODS AUSTRALIA PTY LTD</t>
+        </is>
+      </c>
+      <c r="B313" s="7" t="inlineStr"/>
+      <c r="C313" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D313" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="7" t="inlineStr">
+        <is>
+          <t>Saltbush Livestock Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B314" s="7" t="inlineStr"/>
+      <c r="C314" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D314" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B315" s="7" t="inlineStr"/>
+      <c r="C315" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D315" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B316" s="7" t="inlineStr">
+        <is>
+          <t>Judsonodgers@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C316" s="7" t="inlineStr"/>
+      <c r="D316" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B317" s="7" t="inlineStr">
+        <is>
+          <t>adhamamyra@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C317" s="7" t="inlineStr"/>
+      <c r="D317" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B318" s="7" t="inlineStr">
+        <is>
+          <t>anhta@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C318" s="7" t="inlineStr"/>
+      <c r="D318" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B319" s="7" t="inlineStr">
+        <is>
+          <t>ausland@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C319" s="7" t="inlineStr"/>
+      <c r="D319" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B320" s="7" t="inlineStr">
+        <is>
+          <t>davidmccouaig@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C320" s="7" t="inlineStr"/>
+      <c r="D320" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B321" s="7" t="inlineStr">
+        <is>
+          <t>finance@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="inlineStr"/>
+      <c r="D321" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B322" s="7" t="inlineStr">
+        <is>
+          <t>garymarriott@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C322" s="7" t="inlineStr"/>
+      <c r="D322" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B323" s="7" t="inlineStr">
+        <is>
+          <t>hanatrinh@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C323" s="7" t="inlineStr"/>
+      <c r="D323" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B324" s="7" t="inlineStr">
+        <is>
+          <t>john.ausland@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C324" s="7" t="inlineStr"/>
+      <c r="D324" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B325" s="7" t="inlineStr">
+        <is>
+          <t>jonmander@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C325" s="7" t="inlineStr"/>
+      <c r="D325" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B326" s="7" t="inlineStr">
+        <is>
+          <t>jordanlysy@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C326" s="7" t="inlineStr"/>
+      <c r="D326" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B327" s="7" t="inlineStr">
+        <is>
+          <t>justin.ausland@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C327" s="7" t="inlineStr"/>
+      <c r="D327" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B328" s="7" t="inlineStr">
+        <is>
+          <t>justinmahony@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C328" s="7" t="inlineStr"/>
+      <c r="D328" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B329" s="7" t="inlineStr">
+        <is>
+          <t>louisebridgewater@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C329" s="7" t="inlineStr"/>
+      <c r="D329" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B330" s="7" t="inlineStr">
+        <is>
+          <t>magdalena@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C330" s="7" t="inlineStr"/>
+      <c r="D330" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B331" s="7" t="inlineStr">
+        <is>
+          <t>sales@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C331" s="7" t="inlineStr"/>
+      <c r="D331" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B332" s="7" t="inlineStr">
+        <is>
+          <t>samex@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C332" s="7" t="inlineStr"/>
+      <c r="D332" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B333" s="7" t="inlineStr">
+        <is>
+          <t>sammarriott@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C333" s="7" t="inlineStr"/>
+      <c r="D333" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B334" s="7" t="inlineStr">
+        <is>
+          <t>shannontiedtke@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C334" s="7" t="inlineStr"/>
+      <c r="D334" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B335" s="7" t="inlineStr">
+        <is>
+          <t>shipping@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C335" s="7" t="inlineStr"/>
+      <c r="D335" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B336" s="7" t="inlineStr">
+        <is>
+          <t>simonlinke@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C336" s="7" t="inlineStr"/>
+      <c r="D336" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B337" s="7" t="inlineStr">
+        <is>
+          <t>sommerrobson@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C337" s="7" t="inlineStr"/>
+      <c r="D337" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t>valerieyang@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C338" s="7" t="inlineStr"/>
+      <c r="D338" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B339" s="7" t="inlineStr">
+        <is>
+          <t>winniedasilva@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C339" s="7" t="inlineStr"/>
+      <c r="D339" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="7" t="inlineStr">
+        <is>
+          <t>Samex Australian Meat Co Pty L</t>
+        </is>
+      </c>
+      <c r="B340" s="7" t="inlineStr">
+        <is>
+          <t>yoyentaasan@samex.com.au</t>
+        </is>
+      </c>
+      <c r="C340" s="7" t="inlineStr"/>
+      <c r="D340" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="7" t="inlineStr">
+        <is>
+          <t>Security Foods Exports Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B341" s="7" t="inlineStr"/>
+      <c r="C341" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D341" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="7" t="inlineStr">
+        <is>
+          <t>Security Foods Exports Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B342" s="7" t="inlineStr">
+        <is>
+          <t>info@securityfoods.com</t>
+        </is>
+      </c>
+      <c r="C342" s="7" t="inlineStr"/>
+      <c r="D342" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="7" t="inlineStr">
+        <is>
+          <t>Signature Beef Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B343" s="7" t="inlineStr"/>
+      <c r="C343" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D343" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="7" t="inlineStr">
+        <is>
+          <t>Silverfield Enterprises</t>
+        </is>
+      </c>
+      <c r="B344" s="7" t="inlineStr"/>
+      <c r="C344" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D344" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>Simplot Australia Pty ltd</t>
+        </is>
+      </c>
+      <c r="B345" s="7" t="inlineStr"/>
+      <c r="C345" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D345" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="7" t="inlineStr">
+        <is>
+          <t>Southland (Australia) Pty Limited</t>
+        </is>
+      </c>
+      <c r="B346" s="7" t="inlineStr"/>
+      <c r="C346" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D346" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="7" t="inlineStr">
+        <is>
+          <t>Stockyard Beef Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B347" s="7" t="inlineStr"/>
+      <c r="C347" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D347" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="7" t="inlineStr">
+        <is>
+          <t>Stockyard Beef Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B348" s="7" t="inlineStr">
+        <is>
+          <t>info@stockyardbeef.com.au</t>
+        </is>
+      </c>
+      <c r="C348" s="7" t="inlineStr"/>
+      <c r="D348" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="7" t="inlineStr">
+        <is>
+          <t>Stockyard Beef Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B349" s="7" t="inlineStr">
+        <is>
+          <t>kerwee@stockyardbeef.com.au</t>
+        </is>
+      </c>
+      <c r="C349" s="7" t="inlineStr"/>
+      <c r="D349" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="7" t="inlineStr">
+        <is>
+          <t>Subast Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B350" s="7" t="inlineStr"/>
+      <c r="C350" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D350" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="7" t="inlineStr">
+        <is>
+          <t>Swift &amp; Company Trade Group</t>
+        </is>
+      </c>
+      <c r="B351" s="7" t="inlineStr"/>
+      <c r="C351" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D351" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="7" t="inlineStr">
+        <is>
+          <t>THE TRUSTEE FOR JFW ENTERPRISES TRUST</t>
+        </is>
+      </c>
+      <c r="B352" s="7" t="inlineStr"/>
+      <c r="C352" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D352" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="7" t="inlineStr">
+        <is>
+          <t>TOP CUT FOOD INDUSTRIES PTY LTD</t>
+        </is>
+      </c>
+      <c r="B353" s="7" t="inlineStr"/>
+      <c r="C353" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D353" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="7" t="inlineStr">
+        <is>
+          <t>Tasmanian Quality Meats</t>
+        </is>
+      </c>
+      <c r="B354" s="7" t="inlineStr"/>
+      <c r="C354" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D354" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="7" t="inlineStr">
+        <is>
+          <t>Teys Australia Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B355" s="7" t="inlineStr"/>
+      <c r="C355" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D355" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="7" t="inlineStr">
+        <is>
+          <t>The Game Meats Company</t>
+        </is>
+      </c>
+      <c r="B356" s="7" t="inlineStr"/>
+      <c r="C356" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D356" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="7" t="inlineStr">
+        <is>
+          <t>Therfield Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B357" s="7" t="inlineStr"/>
+      <c r="C357" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D357" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="7" t="inlineStr">
+        <is>
+          <t>Tradevine</t>
+        </is>
+      </c>
+      <c r="B358" s="7" t="inlineStr"/>
+      <c r="C358" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D358" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="7" t="inlineStr">
+        <is>
+          <t>Two Rivers Agri Group Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B359" s="7" t="inlineStr"/>
+      <c r="C359" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D359" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="7" t="inlineStr">
+        <is>
+          <t>Two Rivers Agri Group Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B360" s="7" t="inlineStr">
+        <is>
+          <t>export@tworiversagrigroup.com</t>
+        </is>
+      </c>
+      <c r="C360" s="7" t="inlineStr"/>
+      <c r="D360" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="7" t="inlineStr">
+        <is>
+          <t>United World Enterprises Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B361" s="7" t="inlineStr"/>
+      <c r="C361" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D361" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="7" t="inlineStr">
+        <is>
+          <t>VG Food Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B362" s="7" t="inlineStr"/>
+      <c r="C362" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D362" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B363" s="7" t="inlineStr"/>
+      <c r="C363" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D363" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B364" s="7" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C364" s="7" t="inlineStr"/>
+      <c r="D364" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B365" s="7" t="inlineStr">
+        <is>
+          <t>78f7996315bc402f9dcb8a2f974b82d1@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C365" s="7" t="inlineStr"/>
+      <c r="D365" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B366" s="7" t="inlineStr">
+        <is>
+          <t>8c4075d5481d476e945486754f783364@sentry.io</t>
+        </is>
+      </c>
+      <c r="C366" s="7" t="inlineStr"/>
+      <c r="D366" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B367" s="7" t="inlineStr">
+        <is>
+          <t>9a65e97ebe8141fca0c4fd686f70996b@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C367" s="7" t="inlineStr"/>
+      <c r="D367" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B368" s="7" t="inlineStr">
+        <is>
+          <t>info@suzukifarm.com.au</t>
+        </is>
+      </c>
+      <c r="C368" s="7" t="inlineStr"/>
+      <c r="D368" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B369" s="7" t="inlineStr">
+        <is>
+          <t>op@suzukifarm.com.au</t>
+        </is>
+      </c>
+      <c r="C369" s="7" t="inlineStr"/>
+      <c r="D369" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="7" t="inlineStr">
+        <is>
+          <t>W&amp;B Holdings Corporation PTY LTD</t>
+        </is>
+      </c>
+      <c r="B370" s="7" t="inlineStr">
+        <is>
+          <t>sales@suzukifarmwagyu.com</t>
+        </is>
+      </c>
+      <c r="C370" s="7" t="inlineStr"/>
+      <c r="D370" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="7" t="inlineStr">
+        <is>
+          <t>WA Meat Exports</t>
+        </is>
+      </c>
+      <c r="B371" s="7" t="inlineStr"/>
+      <c r="C371" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D371" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="7" t="inlineStr">
+        <is>
+          <t>WARMOLL FOODS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B372" s="7" t="inlineStr"/>
+      <c r="C372" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D372" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B373" s="7" t="inlineStr"/>
+      <c r="C373" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D373" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B374" s="7" t="inlineStr">
+        <is>
+          <t>18d2f96d279149989b95faf0a4b41882@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C374" s="7" t="inlineStr"/>
+      <c r="D374" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B375" s="7" t="inlineStr">
+        <is>
+          <t>463991d7bca24f02a0baf16f9e6eda73@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C375" s="7" t="inlineStr"/>
+      <c r="D375" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B376" s="7" t="inlineStr">
+        <is>
+          <t>5d1795a2db124a268f1e1bd88f503500@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C376" s="7" t="inlineStr"/>
+      <c r="D376" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B377" s="7" t="inlineStr">
+        <is>
+          <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C377" s="7" t="inlineStr"/>
+      <c r="D377" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B378" s="7" t="inlineStr">
+        <is>
+          <t>8eb368c655b84e029ed79ad7a5c1718e@sentry.wixpress.com</t>
+        </is>
+      </c>
+      <c r="C378" s="7" t="inlineStr"/>
+      <c r="D378" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B379" s="7" t="inlineStr">
+        <is>
+          <t>enquiries@westernmeatexporters.com.au</t>
+        </is>
+      </c>
+      <c r="C379" s="7" t="inlineStr"/>
+      <c r="D379" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="7" t="inlineStr">
+        <is>
+          <t>WESTERN MEAT EXPORTERS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B380" s="7" t="inlineStr">
+        <is>
+          <t>example@mysite.com</t>
+        </is>
+      </c>
+      <c r="C380" s="7" t="inlineStr"/>
+      <c r="D380" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="7" t="inlineStr">
+        <is>
+          <t>WHITE STRIPE FOODS PTY LTD</t>
+        </is>
+      </c>
+      <c r="B381" s="7" t="inlineStr"/>
+      <c r="C381" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D381" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="7" t="inlineStr">
+        <is>
+          <t>WYLOO PASTORAL COMPANY PTY LTD</t>
+        </is>
+      </c>
+      <c r="B382" s="7" t="inlineStr"/>
+      <c r="C382" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D382" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="7" t="inlineStr">
+        <is>
+          <t>Wingham Beef Exports Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B383" s="7" t="inlineStr"/>
+      <c r="C383" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D383" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="7" t="inlineStr">
+        <is>
+          <t>World Wide Exporters Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B384" s="7" t="inlineStr"/>
+      <c r="C384" s="7" t="inlineStr">
+        <is>
+          <t>+61 02 9463 9333 1800 023 100</t>
+        </is>
+      </c>
+      <c r="D384" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="7" t="inlineStr">
+        <is>
+          <t>World Wide Exporters Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B385" s="7" t="inlineStr">
+        <is>
+          <t>info@wwe.com.au</t>
+        </is>
+      </c>
+      <c r="C385" s="7" t="inlineStr"/>
+      <c r="D385" s="7" t="inlineStr">
+        <is>
+          <t>regex_or_href</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="7" t="inlineStr">
+        <is>
           <t>Yuggera Trading Pty Ltd</t>
         </is>
       </c>
-      <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="7" t="inlineStr">
+      <c r="B386" s="7" t="inlineStr"/>
+      <c r="C386" s="7" t="inlineStr">
         <is>
           <t>+61 02 9463 9333 1800 023 100</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr">
+      <c r="D386" s="7" t="inlineStr">
         <is>
           <t>regex_or_href</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D160"/>
+  <autoFilter ref="A1:D386"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/exporters_master.xlsx
+++ b/exporters_master.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08T22:46:55+00:00</t>
+          <t>2026-06-09T13:07:10+00:00</t>
         </is>
       </c>
     </row>
